--- a/Entregables/CasosDeUso.xlsx
+++ b/Entregables/CasosDeUso.xlsx
@@ -1,13 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andressiqueiros/Downloads/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DC9577E0-D407-C246-8286-BDE2929811E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16260" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Analisis de Riesgo" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="Casos de Uso" sheetId="2" r:id="rId6"/>
+    <sheet name="Analisis de Riesgo" sheetId="1" r:id="rId1"/>
+    <sheet name="Casos de Uso" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -147,24 +156,30 @@
   <si>
     <r>
       <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">1. Actor selecciona “Agregar libro”.
 2. Completa campos: título, autor(es), ISBN, editorial, año, categoría, número de copias, ubicación física, sinopsis, </t>
     </r>
     <r>
       <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <b/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">status </t>
     </r>
     <r>
       <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t>(Disponible, Colección, Reserva, No Disponible).
 3. Presiona “Guardar”.
@@ -303,14 +318,6 @@
  4. Sin multas pendientes.</t>
   </si>
   <si>
-    <t>1. Usuario accede a 'Mis Préstamos'.
- 2. Selecciona el préstamo a renovar.
- 3. Presiona 'Renovar Préstamo'.
- 4. Sistema verifica que no haya lista de espera.
- 5. Sistema extiende la fecha de vencimiento según política.
- 6. Sistema notifica al usuario la nueva fecha límite.</t>
-  </si>
-  <si>
     <t>A1: Préstamo vencido — redirige al flujo de devolución con multa.
  A2: Libro en lista de espera — no permite renovación.
  A3: Máximo de renovaciones alcanzado — solicita devolución.
@@ -347,15 +354,6 @@
   <si>
     <t>1. Préstamo activo registrado en el sistema.
  2. Usuario autenticado con el préstamo a su nombre.</t>
-  </si>
-  <si>
-    <t>1. Usuario accede a 'Mis Préstamos' y selecciona el préstamo.
- 2. Presiona 'Registrar Devolución'.
- 3. Sistema calcula si existe retraso.
- 4. Si no hay retraso, registra devolución y libera el ejemplar.
- 5. Inventario actualizado: ejemplar disponible.
- 6. Sistema emite comprobante de devolución.
- 7. Notifica a Tesorería si aplica cargo.</t>
   </si>
   <si>
     <t>A1: Devolución tardía — calcula multa y notifica a Tesorería.
@@ -415,40 +413,81 @@
   <si>
     <t>Estado de multa actualizado. Tesorería notificada. Restricciones del usuario ajustadas según estado.</t>
   </si>
+  <si>
+    <t>1. Usuario accede a 'Mis Préstamos'.
+ 2. Selecciona el préstamo a renovar.
+ 3. Presiona 'Renovar Préstamo'.
+ 4. Sistema verifica que no haya lista de espera.
+ 5. Se hace una solicitud a un administrador para aceptar renovacion.
+ 6. Sistema notifica respuesta a solicitud.</t>
+  </si>
+  <si>
+    <t>1. Usuario (Estudiante no) accede a 'manejo de Préstamos' y selecciona el préstamo.
+ 2. Presiona 'Registrar Devolución'.
+ 3. Sistema calcula si existe retraso.
+ 4. Si no hay retraso, registra devolución y libera el ejemplar.
+ 5. Inventario actualizado: ejemplar disponible.
+ 6. Sistema emite comprobante de devolución.
+ 7. Notifica a Tesorería si aplica cargo.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font/>
     <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="9">
@@ -456,7 +495,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -496,13 +535,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="0"/>
         <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="6">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -516,6 +561,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -527,6 +573,8 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -535,9 +583,11 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -546,76 +596,85 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="18">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="2" fillId="6" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="7" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="8" fontId="2" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
-    <xf borderId="2" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -626,20 +685,32 @@
     <xdr:ext cx="3371850" cy="1466850"/>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="2" name="Shape 2" title="Drawing"/>
+        <xdr:cNvPr id="2" name="Shape 2" title="Drawing">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGrpSpPr/>
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="164375" y="531500"/>
-          <a:ext cx="5524300" cy="2380175"/>
+          <a:off x="796018" y="267154"/>
+          <a:ext cx="3371850" cy="1466850"/>
           <a:chOff x="164375" y="531500"/>
           <a:chExt cx="5524300" cy="2380175"/>
         </a:xfrm>
       </xdr:grpSpPr>
-      <xdr:sp>
+      <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="3" name="Shape 3"/>
+          <xdr:cNvPr id="3" name="Shape 3">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr/>
         </xdr:nvSpPr>
         <xdr:spPr>
@@ -653,23 +724,23 @@
           <a:solidFill>
             <a:srgbClr val="FFFFFF"/>
           </a:solidFill>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="sm" w="sm" type="none"/>
-            <a:tailEnd len="sm" w="sm" type="none"/>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="sm" len="sm"/>
+            <a:tailEnd type="none" w="sm" len="sm"/>
           </a:ln>
         </xdr:spPr>
         <xdr:txBody>
-          <a:bodyPr anchorCtr="0" anchor="ctr" bIns="91425" lIns="91425" spcFirstLastPara="1" rIns="91425" wrap="square" tIns="91425">
+          <a:bodyPr spcFirstLastPara="1" wrap="square" lIns="91425" tIns="91425" rIns="91425" bIns="91425" anchor="ctr" anchorCtr="0">
             <a:noAutofit/>
           </a:bodyPr>
           <a:lstStyle/>
           <a:p>
-            <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="ctr">
+            <a:pPr marL="0" lvl="0" indent="0" algn="ctr" rtl="0">
               <a:spcBef>
                 <a:spcPts val="0"/>
               </a:spcBef>
@@ -678,16 +749,19 @@
               </a:spcAft>
               <a:buNone/>
             </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
             <a:endParaRPr sz="1400"/>
           </a:p>
         </xdr:txBody>
       </xdr:sp>
-      <xdr:cxnSp>
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="4" name="Shape 4"/>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="4" name="Shape 4">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000004000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvCxnSpPr>
             <a:stCxn id="3" idx="4"/>
           </xdr:cNvCxnSpPr>
@@ -701,20 +775,26 @@
             <a:avLst/>
           </a:prstGeom>
           <a:noFill/>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="med" w="med" type="none"/>
-            <a:tailEnd len="med" w="med" type="none"/>
-          </a:ln>
-        </xdr:spPr>
-      </xdr:cxnSp>
-      <xdr:cxnSp>
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="5" name="Shape 5"/>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="med" len="med"/>
+            <a:tailEnd type="none" w="med" len="med"/>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="5" name="Shape 5">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000005000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvCxnSpPr/>
         </xdr:nvCxnSpPr>
         <xdr:spPr>
@@ -726,20 +806,26 @@
             <a:avLst/>
           </a:prstGeom>
           <a:noFill/>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="med" w="med" type="none"/>
-            <a:tailEnd len="med" w="med" type="none"/>
-          </a:ln>
-        </xdr:spPr>
-      </xdr:cxnSp>
-      <xdr:cxnSp>
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="6" name="Shape 6"/>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="med" len="med"/>
+            <a:tailEnd type="none" w="med" len="med"/>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="6" name="Shape 6">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000006000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvCxnSpPr/>
         </xdr:nvCxnSpPr>
         <xdr:spPr>
@@ -751,20 +837,26 @@
             <a:avLst/>
           </a:prstGeom>
           <a:noFill/>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="med" w="med" type="none"/>
-            <a:tailEnd len="med" w="med" type="none"/>
-          </a:ln>
-        </xdr:spPr>
-      </xdr:cxnSp>
-      <xdr:cxnSp>
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="7" name="Shape 7"/>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="med" len="med"/>
+            <a:tailEnd type="none" w="med" len="med"/>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="7" name="Shape 7">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000007000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvCxnSpPr/>
         </xdr:nvCxnSpPr>
         <xdr:spPr>
@@ -776,20 +868,26 @@
             <a:avLst/>
           </a:prstGeom>
           <a:noFill/>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="med" w="med" type="none"/>
-            <a:tailEnd len="med" w="med" type="none"/>
-          </a:ln>
-        </xdr:spPr>
-      </xdr:cxnSp>
-      <xdr:sp>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="med" len="med"/>
+            <a:tailEnd type="none" w="med" len="med"/>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:cxnSp>
+      <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="8" name="Shape 8"/>
+          <xdr:cNvPr id="8" name="Shape 8">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000008000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr/>
         </xdr:nvSpPr>
         <xdr:spPr>
@@ -801,23 +899,23 @@
             <a:avLst/>
           </a:prstGeom>
           <a:noFill/>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="sm" w="sm" type="none"/>
-            <a:tailEnd len="sm" w="sm" type="none"/>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="sm" len="sm"/>
+            <a:tailEnd type="none" w="sm" len="sm"/>
           </a:ln>
         </xdr:spPr>
         <xdr:txBody>
-          <a:bodyPr anchorCtr="0" anchor="ctr" bIns="91425" lIns="91425" spcFirstLastPara="1" rIns="91425" wrap="square" tIns="91425">
+          <a:bodyPr spcFirstLastPara="1" wrap="square" lIns="91425" tIns="91425" rIns="91425" bIns="91425" anchor="ctr" anchorCtr="0">
             <a:noAutofit/>
           </a:bodyPr>
           <a:lstStyle/>
           <a:p>
-            <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="ctr">
+            <a:pPr marL="0" lvl="0" indent="0" algn="ctr" rtl="0">
               <a:spcBef>
                 <a:spcPts val="0"/>
               </a:spcBef>
@@ -834,9 +932,15 @@
           </a:p>
         </xdr:txBody>
       </xdr:sp>
-      <xdr:sp>
+      <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="9" name="Shape 9"/>
+          <xdr:cNvPr id="9" name="Shape 9">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000009000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr txBox="1"/>
         </xdr:nvSpPr>
         <xdr:spPr>
@@ -853,12 +957,12 @@
           </a:ln>
         </xdr:spPr>
         <xdr:txBody>
-          <a:bodyPr anchorCtr="0" anchor="t" bIns="91425" lIns="91425" spcFirstLastPara="1" rIns="91425" wrap="square" tIns="91425">
+          <a:bodyPr spcFirstLastPara="1" wrap="square" lIns="91425" tIns="91425" rIns="91425" bIns="91425" anchor="t" anchorCtr="0">
             <a:noAutofit/>
           </a:bodyPr>
           <a:lstStyle/>
           <a:p>
-            <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+            <a:pPr marL="0" lvl="0" indent="0" algn="l" rtl="0">
               <a:spcBef>
                 <a:spcPts val="0"/>
               </a:spcBef>
@@ -875,9 +979,15 @@
           </a:p>
         </xdr:txBody>
       </xdr:sp>
-      <xdr:sp>
+      <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="10" name="Shape 10"/>
+          <xdr:cNvPr id="10" name="Shape 10">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000A000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr/>
         </xdr:nvSpPr>
         <xdr:spPr>
@@ -891,23 +1001,23 @@
           <a:solidFill>
             <a:srgbClr val="FFFFFF"/>
           </a:solidFill>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="sm" w="sm" type="none"/>
-            <a:tailEnd len="sm" w="sm" type="none"/>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="sm" len="sm"/>
+            <a:tailEnd type="none" w="sm" len="sm"/>
           </a:ln>
         </xdr:spPr>
         <xdr:txBody>
-          <a:bodyPr anchorCtr="0" anchor="ctr" bIns="91425" lIns="91425" spcFirstLastPara="1" rIns="91425" wrap="square" tIns="91425">
+          <a:bodyPr spcFirstLastPara="1" wrap="square" lIns="91425" tIns="91425" rIns="91425" bIns="91425" anchor="ctr" anchorCtr="0">
             <a:noAutofit/>
           </a:bodyPr>
           <a:lstStyle/>
           <a:p>
-            <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="ctr">
+            <a:pPr marL="0" lvl="0" indent="0" algn="ctr" rtl="0">
               <a:spcBef>
                 <a:spcPts val="0"/>
               </a:spcBef>
@@ -916,16 +1026,19 @@
               </a:spcAft>
               <a:buNone/>
             </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
             <a:endParaRPr sz="1400"/>
           </a:p>
         </xdr:txBody>
       </xdr:sp>
-      <xdr:cxnSp>
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="11" name="Shape 11"/>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="11" name="Shape 11">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000B000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvCxnSpPr>
             <a:stCxn id="10" idx="4"/>
           </xdr:cNvCxnSpPr>
@@ -939,20 +1052,26 @@
             <a:avLst/>
           </a:prstGeom>
           <a:noFill/>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="med" w="med" type="none"/>
-            <a:tailEnd len="med" w="med" type="none"/>
-          </a:ln>
-        </xdr:spPr>
-      </xdr:cxnSp>
-      <xdr:cxnSp>
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="12" name="Shape 12"/>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="med" len="med"/>
+            <a:tailEnd type="none" w="med" len="med"/>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="12" name="Shape 12">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000C000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvCxnSpPr/>
         </xdr:nvCxnSpPr>
         <xdr:spPr>
@@ -964,20 +1083,26 @@
             <a:avLst/>
           </a:prstGeom>
           <a:noFill/>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="med" w="med" type="none"/>
-            <a:tailEnd len="med" w="med" type="none"/>
-          </a:ln>
-        </xdr:spPr>
-      </xdr:cxnSp>
-      <xdr:cxnSp>
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="13" name="Shape 13"/>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="med" len="med"/>
+            <a:tailEnd type="none" w="med" len="med"/>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="13" name="Shape 13">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000D000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvCxnSpPr/>
         </xdr:nvCxnSpPr>
         <xdr:spPr>
@@ -989,20 +1114,26 @@
             <a:avLst/>
           </a:prstGeom>
           <a:noFill/>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="med" w="med" type="none"/>
-            <a:tailEnd len="med" w="med" type="none"/>
-          </a:ln>
-        </xdr:spPr>
-      </xdr:cxnSp>
-      <xdr:cxnSp>
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="14" name="Shape 14"/>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="med" len="med"/>
+            <a:tailEnd type="none" w="med" len="med"/>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="14" name="Shape 14">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000E000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvCxnSpPr/>
         </xdr:nvCxnSpPr>
         <xdr:spPr>
@@ -1014,20 +1145,26 @@
             <a:avLst/>
           </a:prstGeom>
           <a:noFill/>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="med" w="med" type="none"/>
-            <a:tailEnd len="med" w="med" type="none"/>
-          </a:ln>
-        </xdr:spPr>
-      </xdr:cxnSp>
-      <xdr:sp>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="med" len="med"/>
+            <a:tailEnd type="none" w="med" len="med"/>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:cxnSp>
+      <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="15" name="Shape 15"/>
+          <xdr:cNvPr id="15" name="Shape 15">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000F000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr txBox="1"/>
         </xdr:nvSpPr>
         <xdr:spPr>
@@ -1044,12 +1181,12 @@
           </a:ln>
         </xdr:spPr>
         <xdr:txBody>
-          <a:bodyPr anchorCtr="0" anchor="t" bIns="91425" lIns="91425" spcFirstLastPara="1" rIns="91425" wrap="square" tIns="91425">
+          <a:bodyPr spcFirstLastPara="1" wrap="square" lIns="91425" tIns="91425" rIns="91425" bIns="91425" anchor="t" anchorCtr="0">
             <a:noAutofit/>
           </a:bodyPr>
           <a:lstStyle/>
           <a:p>
-            <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+            <a:pPr marL="0" lvl="0" indent="0" algn="l" rtl="0">
               <a:spcBef>
                 <a:spcPts val="0"/>
               </a:spcBef>
@@ -1066,9 +1203,15 @@
           </a:p>
         </xdr:txBody>
       </xdr:sp>
-      <xdr:cxnSp>
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="16" name="Shape 16"/>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="16" name="Shape 16">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000010000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvCxnSpPr/>
         </xdr:nvCxnSpPr>
         <xdr:spPr>
@@ -1080,20 +1223,26 @@
             <a:avLst/>
           </a:prstGeom>
           <a:noFill/>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="med" w="med" type="none"/>
-            <a:tailEnd len="med" w="med" type="none"/>
-          </a:ln>
-        </xdr:spPr>
-      </xdr:cxnSp>
-      <xdr:cxnSp>
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="17" name="Shape 17"/>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="med" len="med"/>
+            <a:tailEnd type="none" w="med" len="med"/>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="17" name="Shape 17">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000011000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvCxnSpPr/>
         </xdr:nvCxnSpPr>
         <xdr:spPr>
@@ -1105,14 +1254,14 @@
             <a:avLst/>
           </a:prstGeom>
           <a:noFill/>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="med" w="med" type="none"/>
-            <a:tailEnd len="med" w="med" type="none"/>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="med" len="med"/>
+            <a:tailEnd type="none" w="med" len="med"/>
           </a:ln>
         </xdr:spPr>
       </xdr:cxnSp>
@@ -1129,20 +1278,32 @@
     <xdr:ext cx="2447925" cy="2171700"/>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="2" name="Shape 2" title="Dibujo"/>
+        <xdr:cNvPr id="18" name="Shape 2" title="Dibujo">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000012000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGrpSpPr/>
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="164375" y="531500"/>
-          <a:ext cx="5432950" cy="4816550"/>
+          <a:off x="1177018" y="2038804"/>
+          <a:ext cx="2447925" cy="2171700"/>
           <a:chOff x="164375" y="531500"/>
           <a:chExt cx="5432950" cy="4816550"/>
         </a:xfrm>
       </xdr:grpSpPr>
-      <xdr:sp>
+      <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="18" name="Shape 18"/>
+          <xdr:cNvPr id="19" name="Shape 18">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000013000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr/>
         </xdr:nvSpPr>
         <xdr:spPr>
@@ -1156,23 +1317,23 @@
           <a:solidFill>
             <a:srgbClr val="FFFFFF"/>
           </a:solidFill>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="sm" w="sm" type="none"/>
-            <a:tailEnd len="sm" w="sm" type="none"/>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="sm" len="sm"/>
+            <a:tailEnd type="none" w="sm" len="sm"/>
           </a:ln>
         </xdr:spPr>
         <xdr:txBody>
-          <a:bodyPr anchorCtr="0" anchor="ctr" bIns="91425" lIns="91425" spcFirstLastPara="1" rIns="91425" wrap="square" tIns="91425">
+          <a:bodyPr spcFirstLastPara="1" wrap="square" lIns="91425" tIns="91425" rIns="91425" bIns="91425" anchor="ctr" anchorCtr="0">
             <a:noAutofit/>
           </a:bodyPr>
           <a:lstStyle/>
           <a:p>
-            <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="ctr">
+            <a:pPr marL="0" lvl="0" indent="0" algn="ctr" rtl="0">
               <a:spcBef>
                 <a:spcPts val="0"/>
               </a:spcBef>
@@ -1181,16 +1342,19 @@
               </a:spcAft>
               <a:buNone/>
             </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
             <a:endParaRPr sz="1400"/>
           </a:p>
         </xdr:txBody>
       </xdr:sp>
-      <xdr:cxnSp>
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="19" name="Shape 19"/>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="20" name="Shape 19">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000014000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvCxnSpPr>
             <a:stCxn id="18" idx="4"/>
           </xdr:cNvCxnSpPr>
@@ -1204,20 +1368,26 @@
             <a:avLst/>
           </a:prstGeom>
           <a:noFill/>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="med" w="med" type="none"/>
-            <a:tailEnd len="med" w="med" type="none"/>
-          </a:ln>
-        </xdr:spPr>
-      </xdr:cxnSp>
-      <xdr:cxnSp>
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="20" name="Shape 20"/>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="med" len="med"/>
+            <a:tailEnd type="none" w="med" len="med"/>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="21" name="Shape 20">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000015000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvCxnSpPr/>
         </xdr:nvCxnSpPr>
         <xdr:spPr>
@@ -1229,20 +1399,26 @@
             <a:avLst/>
           </a:prstGeom>
           <a:noFill/>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="med" w="med" type="none"/>
-            <a:tailEnd len="med" w="med" type="none"/>
-          </a:ln>
-        </xdr:spPr>
-      </xdr:cxnSp>
-      <xdr:cxnSp>
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="21" name="Shape 21"/>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="med" len="med"/>
+            <a:tailEnd type="none" w="med" len="med"/>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="22" name="Shape 21">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000016000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvCxnSpPr/>
         </xdr:nvCxnSpPr>
         <xdr:spPr>
@@ -1254,20 +1430,26 @@
             <a:avLst/>
           </a:prstGeom>
           <a:noFill/>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="med" w="med" type="none"/>
-            <a:tailEnd len="med" w="med" type="none"/>
-          </a:ln>
-        </xdr:spPr>
-      </xdr:cxnSp>
-      <xdr:cxnSp>
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="22" name="Shape 22"/>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="med" len="med"/>
+            <a:tailEnd type="none" w="med" len="med"/>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="23" name="Shape 22">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000017000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvCxnSpPr/>
         </xdr:nvCxnSpPr>
         <xdr:spPr>
@@ -1279,20 +1461,26 @@
             <a:avLst/>
           </a:prstGeom>
           <a:noFill/>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="med" w="med" type="none"/>
-            <a:tailEnd len="med" w="med" type="none"/>
-          </a:ln>
-        </xdr:spPr>
-      </xdr:cxnSp>
-      <xdr:sp>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="med" len="med"/>
+            <a:tailEnd type="none" w="med" len="med"/>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:cxnSp>
+      <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="23" name="Shape 23"/>
+          <xdr:cNvPr id="24" name="Shape 23">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000018000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr/>
         </xdr:nvSpPr>
         <xdr:spPr>
@@ -1304,23 +1492,23 @@
             <a:avLst/>
           </a:prstGeom>
           <a:noFill/>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="sm" w="sm" type="none"/>
-            <a:tailEnd len="sm" w="sm" type="none"/>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="sm" len="sm"/>
+            <a:tailEnd type="none" w="sm" len="sm"/>
           </a:ln>
         </xdr:spPr>
         <xdr:txBody>
-          <a:bodyPr anchorCtr="0" anchor="ctr" bIns="91425" lIns="91425" spcFirstLastPara="1" rIns="91425" wrap="square" tIns="91425">
+          <a:bodyPr spcFirstLastPara="1" wrap="square" lIns="91425" tIns="91425" rIns="91425" bIns="91425" anchor="ctr" anchorCtr="0">
             <a:noAutofit/>
           </a:bodyPr>
           <a:lstStyle/>
           <a:p>
-            <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="ctr">
+            <a:pPr marL="0" lvl="0" indent="0" algn="ctr" rtl="0">
               <a:spcBef>
                 <a:spcPts val="0"/>
               </a:spcBef>
@@ -1337,9 +1525,15 @@
           </a:p>
         </xdr:txBody>
       </xdr:sp>
-      <xdr:sp>
+      <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="24" name="Shape 24"/>
+          <xdr:cNvPr id="25" name="Shape 24">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000019000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr txBox="1"/>
         </xdr:nvSpPr>
         <xdr:spPr>
@@ -1356,12 +1550,12 @@
           </a:ln>
         </xdr:spPr>
         <xdr:txBody>
-          <a:bodyPr anchorCtr="0" anchor="t" bIns="91425" lIns="91425" spcFirstLastPara="1" rIns="91425" wrap="square" tIns="91425">
+          <a:bodyPr spcFirstLastPara="1" wrap="square" lIns="91425" tIns="91425" rIns="91425" bIns="91425" anchor="t" anchorCtr="0">
             <a:noAutofit/>
           </a:bodyPr>
           <a:lstStyle/>
           <a:p>
-            <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+            <a:pPr marL="0" lvl="0" indent="0" algn="l" rtl="0">
               <a:spcBef>
                 <a:spcPts val="0"/>
               </a:spcBef>
@@ -1378,9 +1572,15 @@
           </a:p>
         </xdr:txBody>
       </xdr:sp>
-      <xdr:sp>
+      <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="25" name="Shape 25"/>
+          <xdr:cNvPr id="26" name="Shape 25">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00001A000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr/>
         </xdr:nvSpPr>
         <xdr:spPr>
@@ -1394,23 +1594,23 @@
           <a:solidFill>
             <a:srgbClr val="FFFFFF"/>
           </a:solidFill>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="sm" w="sm" type="none"/>
-            <a:tailEnd len="sm" w="sm" type="none"/>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="sm" len="sm"/>
+            <a:tailEnd type="none" w="sm" len="sm"/>
           </a:ln>
         </xdr:spPr>
         <xdr:txBody>
-          <a:bodyPr anchorCtr="0" anchor="ctr" bIns="91425" lIns="91425" spcFirstLastPara="1" rIns="91425" wrap="square" tIns="91425">
+          <a:bodyPr spcFirstLastPara="1" wrap="square" lIns="91425" tIns="91425" rIns="91425" bIns="91425" anchor="ctr" anchorCtr="0">
             <a:noAutofit/>
           </a:bodyPr>
           <a:lstStyle/>
           <a:p>
-            <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="ctr">
+            <a:pPr marL="0" lvl="0" indent="0" algn="ctr" rtl="0">
               <a:spcBef>
                 <a:spcPts val="0"/>
               </a:spcBef>
@@ -1419,16 +1619,19 @@
               </a:spcAft>
               <a:buNone/>
             </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
             <a:endParaRPr sz="1400"/>
           </a:p>
         </xdr:txBody>
       </xdr:sp>
-      <xdr:cxnSp>
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="26" name="Shape 26"/>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="27" name="Shape 26">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00001B000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvCxnSpPr>
             <a:stCxn id="25" idx="4"/>
           </xdr:cNvCxnSpPr>
@@ -1442,20 +1645,26 @@
             <a:avLst/>
           </a:prstGeom>
           <a:noFill/>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="med" w="med" type="none"/>
-            <a:tailEnd len="med" w="med" type="none"/>
-          </a:ln>
-        </xdr:spPr>
-      </xdr:cxnSp>
-      <xdr:cxnSp>
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="27" name="Shape 27"/>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="med" len="med"/>
+            <a:tailEnd type="none" w="med" len="med"/>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="28" name="Shape 27">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00001C000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvCxnSpPr/>
         </xdr:nvCxnSpPr>
         <xdr:spPr>
@@ -1467,20 +1676,26 @@
             <a:avLst/>
           </a:prstGeom>
           <a:noFill/>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="med" w="med" type="none"/>
-            <a:tailEnd len="med" w="med" type="none"/>
-          </a:ln>
-        </xdr:spPr>
-      </xdr:cxnSp>
-      <xdr:cxnSp>
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="28" name="Shape 28"/>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="med" len="med"/>
+            <a:tailEnd type="none" w="med" len="med"/>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="29" name="Shape 28">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00001D000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvCxnSpPr/>
         </xdr:nvCxnSpPr>
         <xdr:spPr>
@@ -1492,20 +1707,26 @@
             <a:avLst/>
           </a:prstGeom>
           <a:noFill/>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="med" w="med" type="none"/>
-            <a:tailEnd len="med" w="med" type="none"/>
-          </a:ln>
-        </xdr:spPr>
-      </xdr:cxnSp>
-      <xdr:cxnSp>
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="29" name="Shape 29"/>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="med" len="med"/>
+            <a:tailEnd type="none" w="med" len="med"/>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="30" name="Shape 29">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00001E000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvCxnSpPr/>
         </xdr:nvCxnSpPr>
         <xdr:spPr>
@@ -1517,20 +1738,26 @@
             <a:avLst/>
           </a:prstGeom>
           <a:noFill/>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="med" w="med" type="none"/>
-            <a:tailEnd len="med" w="med" type="none"/>
-          </a:ln>
-        </xdr:spPr>
-      </xdr:cxnSp>
-      <xdr:sp>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="med" len="med"/>
+            <a:tailEnd type="none" w="med" len="med"/>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:cxnSp>
+      <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="30" name="Shape 30"/>
+          <xdr:cNvPr id="31" name="Shape 30">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00001F000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr txBox="1"/>
         </xdr:nvSpPr>
         <xdr:spPr>
@@ -1547,12 +1774,12 @@
           </a:ln>
         </xdr:spPr>
         <xdr:txBody>
-          <a:bodyPr anchorCtr="0" anchor="t" bIns="91425" lIns="91425" spcFirstLastPara="1" rIns="91425" wrap="square" tIns="91425">
+          <a:bodyPr spcFirstLastPara="1" wrap="square" lIns="91425" tIns="91425" rIns="91425" bIns="91425" anchor="t" anchorCtr="0">
             <a:noAutofit/>
           </a:bodyPr>
           <a:lstStyle/>
           <a:p>
-            <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+            <a:pPr marL="0" lvl="0" indent="0" algn="l" rtl="0">
               <a:spcBef>
                 <a:spcPts val="0"/>
               </a:spcBef>
@@ -1569,9 +1796,15 @@
           </a:p>
         </xdr:txBody>
       </xdr:sp>
-      <xdr:cxnSp>
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="31" name="Shape 31"/>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="32" name="Shape 31">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000020000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvCxnSpPr/>
         </xdr:nvCxnSpPr>
         <xdr:spPr>
@@ -1583,20 +1816,26 @@
             <a:avLst/>
           </a:prstGeom>
           <a:noFill/>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="med" w="med" type="none"/>
-            <a:tailEnd len="med" w="med" type="none"/>
-          </a:ln>
-        </xdr:spPr>
-      </xdr:cxnSp>
-      <xdr:cxnSp>
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="32" name="Shape 32"/>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="med" len="med"/>
+            <a:tailEnd type="none" w="med" len="med"/>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="33" name="Shape 32">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000021000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvCxnSpPr/>
         </xdr:nvCxnSpPr>
         <xdr:spPr>
@@ -1608,20 +1847,26 @@
             <a:avLst/>
           </a:prstGeom>
           <a:noFill/>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="med" w="med" type="none"/>
-            <a:tailEnd len="med" w="med" type="none"/>
-          </a:ln>
-        </xdr:spPr>
-      </xdr:cxnSp>
-      <xdr:sp>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="med" len="med"/>
+            <a:tailEnd type="none" w="med" len="med"/>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:cxnSp>
+      <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="33" name="Shape 33"/>
+          <xdr:cNvPr id="34" name="Shape 33">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000022000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr/>
         </xdr:nvSpPr>
         <xdr:spPr>
@@ -1635,23 +1880,23 @@
           <a:solidFill>
             <a:srgbClr val="FFFFFF"/>
           </a:solidFill>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="sm" w="sm" type="none"/>
-            <a:tailEnd len="sm" w="sm" type="none"/>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="sm" len="sm"/>
+            <a:tailEnd type="none" w="sm" len="sm"/>
           </a:ln>
         </xdr:spPr>
         <xdr:txBody>
-          <a:bodyPr anchorCtr="0" anchor="ctr" bIns="91425" lIns="91425" spcFirstLastPara="1" rIns="91425" wrap="square" tIns="91425">
+          <a:bodyPr spcFirstLastPara="1" wrap="square" lIns="91425" tIns="91425" rIns="91425" bIns="91425" anchor="ctr" anchorCtr="0">
             <a:noAutofit/>
           </a:bodyPr>
           <a:lstStyle/>
           <a:p>
-            <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="ctr">
+            <a:pPr marL="0" lvl="0" indent="0" algn="ctr" rtl="0">
               <a:spcBef>
                 <a:spcPts val="0"/>
               </a:spcBef>
@@ -1660,16 +1905,19 @@
               </a:spcAft>
               <a:buNone/>
             </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
             <a:endParaRPr sz="1400"/>
           </a:p>
         </xdr:txBody>
       </xdr:sp>
-      <xdr:cxnSp>
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="34" name="Shape 34"/>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="35" name="Shape 34">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000023000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvCxnSpPr>
             <a:stCxn id="33" idx="4"/>
           </xdr:cNvCxnSpPr>
@@ -1683,20 +1931,26 @@
             <a:avLst/>
           </a:prstGeom>
           <a:noFill/>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="med" w="med" type="none"/>
-            <a:tailEnd len="med" w="med" type="none"/>
-          </a:ln>
-        </xdr:spPr>
-      </xdr:cxnSp>
-      <xdr:cxnSp>
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="35" name="Shape 35"/>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="med" len="med"/>
+            <a:tailEnd type="none" w="med" len="med"/>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="36" name="Shape 35">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000024000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvCxnSpPr/>
         </xdr:nvCxnSpPr>
         <xdr:spPr>
@@ -1708,20 +1962,26 @@
             <a:avLst/>
           </a:prstGeom>
           <a:noFill/>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="med" w="med" type="none"/>
-            <a:tailEnd len="med" w="med" type="none"/>
-          </a:ln>
-        </xdr:spPr>
-      </xdr:cxnSp>
-      <xdr:cxnSp>
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="36" name="Shape 36"/>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="med" len="med"/>
+            <a:tailEnd type="none" w="med" len="med"/>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="37" name="Shape 36">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000025000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvCxnSpPr/>
         </xdr:nvCxnSpPr>
         <xdr:spPr>
@@ -1733,20 +1993,26 @@
             <a:avLst/>
           </a:prstGeom>
           <a:noFill/>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="med" w="med" type="none"/>
-            <a:tailEnd len="med" w="med" type="none"/>
-          </a:ln>
-        </xdr:spPr>
-      </xdr:cxnSp>
-      <xdr:cxnSp>
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="37" name="Shape 37"/>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="med" len="med"/>
+            <a:tailEnd type="none" w="med" len="med"/>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="38" name="Shape 37">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000026000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvCxnSpPr/>
         </xdr:nvCxnSpPr>
         <xdr:spPr>
@@ -1758,20 +2024,26 @@
             <a:avLst/>
           </a:prstGeom>
           <a:noFill/>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="med" w="med" type="none"/>
-            <a:tailEnd len="med" w="med" type="none"/>
-          </a:ln>
-        </xdr:spPr>
-      </xdr:cxnSp>
-      <xdr:sp>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="med" len="med"/>
+            <a:tailEnd type="none" w="med" len="med"/>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:cxnSp>
+      <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="38" name="Shape 38"/>
+          <xdr:cNvPr id="39" name="Shape 38">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000027000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr/>
         </xdr:nvSpPr>
         <xdr:spPr>
@@ -1785,23 +2057,23 @@
           <a:solidFill>
             <a:srgbClr val="FFFFFF"/>
           </a:solidFill>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="sm" w="sm" type="none"/>
-            <a:tailEnd len="sm" w="sm" type="none"/>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="sm" len="sm"/>
+            <a:tailEnd type="none" w="sm" len="sm"/>
           </a:ln>
         </xdr:spPr>
         <xdr:txBody>
-          <a:bodyPr anchorCtr="0" anchor="ctr" bIns="91425" lIns="91425" spcFirstLastPara="1" rIns="91425" wrap="square" tIns="91425">
+          <a:bodyPr spcFirstLastPara="1" wrap="square" lIns="91425" tIns="91425" rIns="91425" bIns="91425" anchor="ctr" anchorCtr="0">
             <a:noAutofit/>
           </a:bodyPr>
           <a:lstStyle/>
           <a:p>
-            <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="ctr">
+            <a:pPr marL="0" lvl="0" indent="0" algn="ctr" rtl="0">
               <a:spcBef>
                 <a:spcPts val="0"/>
               </a:spcBef>
@@ -1810,16 +2082,19 @@
               </a:spcAft>
               <a:buNone/>
             </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
             <a:endParaRPr sz="1400"/>
           </a:p>
         </xdr:txBody>
       </xdr:sp>
-      <xdr:cxnSp>
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="39" name="Shape 39"/>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="40" name="Shape 39">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000028000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvCxnSpPr>
             <a:stCxn id="38" idx="4"/>
           </xdr:cNvCxnSpPr>
@@ -1833,20 +2108,26 @@
             <a:avLst/>
           </a:prstGeom>
           <a:noFill/>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="med" w="med" type="none"/>
-            <a:tailEnd len="med" w="med" type="none"/>
-          </a:ln>
-        </xdr:spPr>
-      </xdr:cxnSp>
-      <xdr:cxnSp>
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="40" name="Shape 40"/>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="med" len="med"/>
+            <a:tailEnd type="none" w="med" len="med"/>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="41" name="Shape 40">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000029000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvCxnSpPr/>
         </xdr:nvCxnSpPr>
         <xdr:spPr>
@@ -1858,20 +2139,26 @@
             <a:avLst/>
           </a:prstGeom>
           <a:noFill/>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="med" w="med" type="none"/>
-            <a:tailEnd len="med" w="med" type="none"/>
-          </a:ln>
-        </xdr:spPr>
-      </xdr:cxnSp>
-      <xdr:cxnSp>
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="41" name="Shape 41"/>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="med" len="med"/>
+            <a:tailEnd type="none" w="med" len="med"/>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="42" name="Shape 41">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00002A000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvCxnSpPr/>
         </xdr:nvCxnSpPr>
         <xdr:spPr>
@@ -1883,20 +2170,26 @@
             <a:avLst/>
           </a:prstGeom>
           <a:noFill/>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="med" w="med" type="none"/>
-            <a:tailEnd len="med" w="med" type="none"/>
-          </a:ln>
-        </xdr:spPr>
-      </xdr:cxnSp>
-      <xdr:cxnSp>
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="42" name="Shape 42"/>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="med" len="med"/>
+            <a:tailEnd type="none" w="med" len="med"/>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="43" name="Shape 42">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00002B000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvCxnSpPr/>
         </xdr:nvCxnSpPr>
         <xdr:spPr>
@@ -1908,20 +2201,26 @@
             <a:avLst/>
           </a:prstGeom>
           <a:noFill/>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="med" w="med" type="none"/>
-            <a:tailEnd len="med" w="med" type="none"/>
-          </a:ln>
-        </xdr:spPr>
-      </xdr:cxnSp>
-      <xdr:sp>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="med" len="med"/>
+            <a:tailEnd type="none" w="med" len="med"/>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:cxnSp>
+      <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="43" name="Shape 43"/>
+          <xdr:cNvPr id="44" name="Shape 43">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00002C000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr txBox="1"/>
         </xdr:nvSpPr>
         <xdr:spPr>
@@ -1938,12 +2237,12 @@
           </a:ln>
         </xdr:spPr>
         <xdr:txBody>
-          <a:bodyPr anchorCtr="0" anchor="t" bIns="91425" lIns="91425" spcFirstLastPara="1" rIns="91425" wrap="square" tIns="91425">
+          <a:bodyPr spcFirstLastPara="1" wrap="square" lIns="91425" tIns="91425" rIns="91425" bIns="91425" anchor="t" anchorCtr="0">
             <a:noAutofit/>
           </a:bodyPr>
           <a:lstStyle/>
           <a:p>
-            <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+            <a:pPr marL="0" lvl="0" indent="0" algn="l" rtl="0">
               <a:spcBef>
                 <a:spcPts val="0"/>
               </a:spcBef>
@@ -1960,9 +2259,15 @@
           </a:p>
         </xdr:txBody>
       </xdr:sp>
-      <xdr:sp>
+      <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="44" name="Shape 44"/>
+          <xdr:cNvPr id="45" name="Shape 44">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00002D000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr txBox="1"/>
         </xdr:nvSpPr>
         <xdr:spPr>
@@ -1979,12 +2284,12 @@
           </a:ln>
         </xdr:spPr>
         <xdr:txBody>
-          <a:bodyPr anchorCtr="0" anchor="t" bIns="91425" lIns="91425" spcFirstLastPara="1" rIns="91425" wrap="square" tIns="91425">
+          <a:bodyPr spcFirstLastPara="1" wrap="square" lIns="91425" tIns="91425" rIns="91425" bIns="91425" anchor="t" anchorCtr="0">
             <a:noAutofit/>
           </a:bodyPr>
           <a:lstStyle/>
           <a:p>
-            <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+            <a:pPr marL="0" lvl="0" indent="0" algn="l" rtl="0">
               <a:spcBef>
                 <a:spcPts val="0"/>
               </a:spcBef>
@@ -2001,13 +2306,19 @@
           </a:p>
         </xdr:txBody>
       </xdr:sp>
-      <xdr:cxnSp>
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="45" name="Shape 45"/>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="46" name="Shape 45">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00002E000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvCxnSpPr/>
         </xdr:nvCxnSpPr>
         <xdr:spPr>
-          <a:xfrm flipH="1" rot="10800000">
+          <a:xfrm rot="10800000" flipH="1">
             <a:off x="1963200" y="2308600"/>
             <a:ext cx="324900" cy="527700"/>
           </a:xfrm>
@@ -2015,20 +2326,26 @@
             <a:avLst/>
           </a:prstGeom>
           <a:noFill/>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="med" w="med" type="none"/>
-            <a:tailEnd len="med" w="med" type="none"/>
-          </a:ln>
-        </xdr:spPr>
-      </xdr:cxnSp>
-      <xdr:cxnSp>
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="46" name="Shape 46"/>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="med" len="med"/>
+            <a:tailEnd type="none" w="med" len="med"/>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="47" name="Shape 46">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00002F000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvCxnSpPr/>
         </xdr:nvCxnSpPr>
         <xdr:spPr>
@@ -2040,20 +2357,26 @@
             <a:avLst/>
           </a:prstGeom>
           <a:noFill/>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="med" w="med" type="none"/>
-            <a:tailEnd len="med" w="med" type="none"/>
-          </a:ln>
-        </xdr:spPr>
-      </xdr:cxnSp>
-      <xdr:sp>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="med" len="med"/>
+            <a:tailEnd type="none" w="med" len="med"/>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:cxnSp>
+      <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="47" name="Shape 47"/>
+          <xdr:cNvPr id="48" name="Shape 47">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000030000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr/>
         </xdr:nvSpPr>
         <xdr:spPr>
@@ -2067,23 +2390,23 @@
           <a:solidFill>
             <a:srgbClr val="FFFFFF"/>
           </a:solidFill>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="sm" w="sm" type="none"/>
-            <a:tailEnd len="sm" w="sm" type="none"/>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="sm" len="sm"/>
+            <a:tailEnd type="none" w="sm" len="sm"/>
           </a:ln>
         </xdr:spPr>
         <xdr:txBody>
-          <a:bodyPr anchorCtr="0" anchor="ctr" bIns="91425" lIns="91425" spcFirstLastPara="1" rIns="91425" wrap="square" tIns="91425">
+          <a:bodyPr spcFirstLastPara="1" wrap="square" lIns="91425" tIns="91425" rIns="91425" bIns="91425" anchor="ctr" anchorCtr="0">
             <a:noAutofit/>
           </a:bodyPr>
           <a:lstStyle/>
           <a:p>
-            <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="ctr">
+            <a:pPr marL="0" lvl="0" indent="0" algn="ctr" rtl="0">
               <a:spcBef>
                 <a:spcPts val="0"/>
               </a:spcBef>
@@ -2092,16 +2415,19 @@
               </a:spcAft>
               <a:buNone/>
             </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
             <a:endParaRPr sz="1400"/>
           </a:p>
         </xdr:txBody>
       </xdr:sp>
-      <xdr:cxnSp>
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="48" name="Shape 48"/>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="49" name="Shape 48">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000031000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvCxnSpPr>
             <a:stCxn id="47" idx="4"/>
           </xdr:cNvCxnSpPr>
@@ -2115,20 +2441,26 @@
             <a:avLst/>
           </a:prstGeom>
           <a:noFill/>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="med" w="med" type="none"/>
-            <a:tailEnd len="med" w="med" type="none"/>
-          </a:ln>
-        </xdr:spPr>
-      </xdr:cxnSp>
-      <xdr:cxnSp>
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="49" name="Shape 49"/>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="med" len="med"/>
+            <a:tailEnd type="none" w="med" len="med"/>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="50" name="Shape 49">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000032000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvCxnSpPr/>
         </xdr:nvCxnSpPr>
         <xdr:spPr>
@@ -2140,20 +2472,26 @@
             <a:avLst/>
           </a:prstGeom>
           <a:noFill/>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="med" w="med" type="none"/>
-            <a:tailEnd len="med" w="med" type="none"/>
-          </a:ln>
-        </xdr:spPr>
-      </xdr:cxnSp>
-      <xdr:cxnSp>
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="50" name="Shape 50"/>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="med" len="med"/>
+            <a:tailEnd type="none" w="med" len="med"/>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="51" name="Shape 50">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000033000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvCxnSpPr/>
         </xdr:nvCxnSpPr>
         <xdr:spPr>
@@ -2165,20 +2503,26 @@
             <a:avLst/>
           </a:prstGeom>
           <a:noFill/>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="med" w="med" type="none"/>
-            <a:tailEnd len="med" w="med" type="none"/>
-          </a:ln>
-        </xdr:spPr>
-      </xdr:cxnSp>
-      <xdr:cxnSp>
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="51" name="Shape 51"/>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="med" len="med"/>
+            <a:tailEnd type="none" w="med" len="med"/>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="52" name="Shape 51">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000034000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvCxnSpPr/>
         </xdr:nvCxnSpPr>
         <xdr:spPr>
@@ -2190,20 +2534,26 @@
             <a:avLst/>
           </a:prstGeom>
           <a:noFill/>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="med" w="med" type="none"/>
-            <a:tailEnd len="med" w="med" type="none"/>
-          </a:ln>
-        </xdr:spPr>
-      </xdr:cxnSp>
-      <xdr:cxnSp>
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="52" name="Shape 52"/>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="med" len="med"/>
+            <a:tailEnd type="none" w="med" len="med"/>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="53" name="Shape 52">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000035000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvCxnSpPr/>
         </xdr:nvCxnSpPr>
         <xdr:spPr>
@@ -2215,20 +2565,26 @@
             <a:avLst/>
           </a:prstGeom>
           <a:noFill/>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="med" w="med" type="none"/>
-            <a:tailEnd len="med" w="med" type="none"/>
-          </a:ln>
-        </xdr:spPr>
-      </xdr:cxnSp>
-      <xdr:sp>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="med" len="med"/>
+            <a:tailEnd type="none" w="med" len="med"/>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:cxnSp>
+      <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="53" name="Shape 53"/>
+          <xdr:cNvPr id="54" name="Shape 53">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000036000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr txBox="1"/>
         </xdr:nvSpPr>
         <xdr:spPr>
@@ -2245,12 +2601,12 @@
           </a:ln>
         </xdr:spPr>
         <xdr:txBody>
-          <a:bodyPr anchorCtr="0" anchor="t" bIns="91425" lIns="91425" spcFirstLastPara="1" rIns="91425" wrap="square" tIns="91425">
+          <a:bodyPr spcFirstLastPara="1" wrap="square" lIns="91425" tIns="91425" rIns="91425" bIns="91425" anchor="t" anchorCtr="0">
             <a:noAutofit/>
           </a:bodyPr>
           <a:lstStyle/>
           <a:p>
-            <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+            <a:pPr marL="0" lvl="0" indent="0" algn="l" rtl="0">
               <a:spcBef>
                 <a:spcPts val="0"/>
               </a:spcBef>
@@ -2280,20 +2636,32 @@
     <xdr:ext cx="3162300" cy="2800350"/>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="2" name="Shape 2" title="Dibujo"/>
+        <xdr:cNvPr id="55" name="Shape 2" title="Dibujo">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000037000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGrpSpPr/>
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="164375" y="531500"/>
-          <a:ext cx="5432950" cy="4816550"/>
+          <a:off x="805543" y="11255829"/>
+          <a:ext cx="3162300" cy="2800350"/>
           <a:chOff x="164375" y="531500"/>
           <a:chExt cx="5432950" cy="4816550"/>
         </a:xfrm>
       </xdr:grpSpPr>
-      <xdr:sp>
+      <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="54" name="Shape 54"/>
+          <xdr:cNvPr id="56" name="Shape 54">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000038000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr/>
         </xdr:nvSpPr>
         <xdr:spPr>
@@ -2307,23 +2675,23 @@
           <a:solidFill>
             <a:srgbClr val="FFFFFF"/>
           </a:solidFill>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="sm" w="sm" type="none"/>
-            <a:tailEnd len="sm" w="sm" type="none"/>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="sm" len="sm"/>
+            <a:tailEnd type="none" w="sm" len="sm"/>
           </a:ln>
         </xdr:spPr>
         <xdr:txBody>
-          <a:bodyPr anchorCtr="0" anchor="ctr" bIns="91425" lIns="91425" spcFirstLastPara="1" rIns="91425" wrap="square" tIns="91425">
+          <a:bodyPr spcFirstLastPara="1" wrap="square" lIns="91425" tIns="91425" rIns="91425" bIns="91425" anchor="ctr" anchorCtr="0">
             <a:noAutofit/>
           </a:bodyPr>
           <a:lstStyle/>
           <a:p>
-            <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="ctr">
+            <a:pPr marL="0" lvl="0" indent="0" algn="ctr" rtl="0">
               <a:spcBef>
                 <a:spcPts val="0"/>
               </a:spcBef>
@@ -2332,16 +2700,19 @@
               </a:spcAft>
               <a:buNone/>
             </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
             <a:endParaRPr sz="1400"/>
           </a:p>
         </xdr:txBody>
       </xdr:sp>
-      <xdr:cxnSp>
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="55" name="Shape 55"/>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="57" name="Shape 55">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000039000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvCxnSpPr>
             <a:stCxn id="54" idx="4"/>
           </xdr:cNvCxnSpPr>
@@ -2355,20 +2726,26 @@
             <a:avLst/>
           </a:prstGeom>
           <a:noFill/>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="med" w="med" type="none"/>
-            <a:tailEnd len="med" w="med" type="none"/>
-          </a:ln>
-        </xdr:spPr>
-      </xdr:cxnSp>
-      <xdr:cxnSp>
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="56" name="Shape 56"/>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="med" len="med"/>
+            <a:tailEnd type="none" w="med" len="med"/>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="58" name="Shape 56">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00003A000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvCxnSpPr/>
         </xdr:nvCxnSpPr>
         <xdr:spPr>
@@ -2380,20 +2757,26 @@
             <a:avLst/>
           </a:prstGeom>
           <a:noFill/>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="med" w="med" type="none"/>
-            <a:tailEnd len="med" w="med" type="none"/>
-          </a:ln>
-        </xdr:spPr>
-      </xdr:cxnSp>
-      <xdr:cxnSp>
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="57" name="Shape 57"/>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="med" len="med"/>
+            <a:tailEnd type="none" w="med" len="med"/>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="59" name="Shape 57">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00003B000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvCxnSpPr/>
         </xdr:nvCxnSpPr>
         <xdr:spPr>
@@ -2405,20 +2788,26 @@
             <a:avLst/>
           </a:prstGeom>
           <a:noFill/>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="med" w="med" type="none"/>
-            <a:tailEnd len="med" w="med" type="none"/>
-          </a:ln>
-        </xdr:spPr>
-      </xdr:cxnSp>
-      <xdr:cxnSp>
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="58" name="Shape 58"/>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="med" len="med"/>
+            <a:tailEnd type="none" w="med" len="med"/>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="60" name="Shape 58">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00003C000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvCxnSpPr/>
         </xdr:nvCxnSpPr>
         <xdr:spPr>
@@ -2430,20 +2819,26 @@
             <a:avLst/>
           </a:prstGeom>
           <a:noFill/>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="med" w="med" type="none"/>
-            <a:tailEnd len="med" w="med" type="none"/>
-          </a:ln>
-        </xdr:spPr>
-      </xdr:cxnSp>
-      <xdr:sp>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="med" len="med"/>
+            <a:tailEnd type="none" w="med" len="med"/>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:cxnSp>
+      <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="59" name="Shape 59"/>
+          <xdr:cNvPr id="61" name="Shape 59">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00003D000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr/>
         </xdr:nvSpPr>
         <xdr:spPr>
@@ -2455,23 +2850,23 @@
             <a:avLst/>
           </a:prstGeom>
           <a:noFill/>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="sm" w="sm" type="none"/>
-            <a:tailEnd len="sm" w="sm" type="none"/>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="sm" len="sm"/>
+            <a:tailEnd type="none" w="sm" len="sm"/>
           </a:ln>
         </xdr:spPr>
         <xdr:txBody>
-          <a:bodyPr anchorCtr="0" anchor="ctr" bIns="91425" lIns="91425" spcFirstLastPara="1" rIns="91425" wrap="square" tIns="91425">
+          <a:bodyPr spcFirstLastPara="1" wrap="square" lIns="91425" tIns="91425" rIns="91425" bIns="91425" anchor="ctr" anchorCtr="0">
             <a:noAutofit/>
           </a:bodyPr>
           <a:lstStyle/>
           <a:p>
-            <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="ctr">
+            <a:pPr marL="0" lvl="0" indent="0" algn="ctr" rtl="0">
               <a:spcBef>
                 <a:spcPts val="0"/>
               </a:spcBef>
@@ -2488,9 +2883,15 @@
           </a:p>
         </xdr:txBody>
       </xdr:sp>
-      <xdr:sp>
+      <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="60" name="Shape 60"/>
+          <xdr:cNvPr id="62" name="Shape 60">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00003E000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr txBox="1"/>
         </xdr:nvSpPr>
         <xdr:spPr>
@@ -2507,12 +2908,12 @@
           </a:ln>
         </xdr:spPr>
         <xdr:txBody>
-          <a:bodyPr anchorCtr="0" anchor="t" bIns="91425" lIns="91425" spcFirstLastPara="1" rIns="91425" wrap="square" tIns="91425">
+          <a:bodyPr spcFirstLastPara="1" wrap="square" lIns="91425" tIns="91425" rIns="91425" bIns="91425" anchor="t" anchorCtr="0">
             <a:noAutofit/>
           </a:bodyPr>
           <a:lstStyle/>
           <a:p>
-            <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+            <a:pPr marL="0" lvl="0" indent="0" algn="l" rtl="0">
               <a:spcBef>
                 <a:spcPts val="0"/>
               </a:spcBef>
@@ -2529,9 +2930,15 @@
           </a:p>
         </xdr:txBody>
       </xdr:sp>
-      <xdr:sp>
+      <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="61" name="Shape 61"/>
+          <xdr:cNvPr id="63" name="Shape 61">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00003F000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr/>
         </xdr:nvSpPr>
         <xdr:spPr>
@@ -2545,23 +2952,23 @@
           <a:solidFill>
             <a:srgbClr val="FFFFFF"/>
           </a:solidFill>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="sm" w="sm" type="none"/>
-            <a:tailEnd len="sm" w="sm" type="none"/>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="sm" len="sm"/>
+            <a:tailEnd type="none" w="sm" len="sm"/>
           </a:ln>
         </xdr:spPr>
         <xdr:txBody>
-          <a:bodyPr anchorCtr="0" anchor="ctr" bIns="91425" lIns="91425" spcFirstLastPara="1" rIns="91425" wrap="square" tIns="91425">
+          <a:bodyPr spcFirstLastPara="1" wrap="square" lIns="91425" tIns="91425" rIns="91425" bIns="91425" anchor="ctr" anchorCtr="0">
             <a:noAutofit/>
           </a:bodyPr>
           <a:lstStyle/>
           <a:p>
-            <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="ctr">
+            <a:pPr marL="0" lvl="0" indent="0" algn="ctr" rtl="0">
               <a:spcBef>
                 <a:spcPts val="0"/>
               </a:spcBef>
@@ -2570,16 +2977,19 @@
               </a:spcAft>
               <a:buNone/>
             </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
             <a:endParaRPr sz="1400"/>
           </a:p>
         </xdr:txBody>
       </xdr:sp>
-      <xdr:cxnSp>
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="62" name="Shape 62"/>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="64" name="Shape 62">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000040000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvCxnSpPr>
             <a:stCxn id="61" idx="4"/>
           </xdr:cNvCxnSpPr>
@@ -2593,20 +3003,26 @@
             <a:avLst/>
           </a:prstGeom>
           <a:noFill/>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="med" w="med" type="none"/>
-            <a:tailEnd len="med" w="med" type="none"/>
-          </a:ln>
-        </xdr:spPr>
-      </xdr:cxnSp>
-      <xdr:cxnSp>
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="63" name="Shape 63"/>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="med" len="med"/>
+            <a:tailEnd type="none" w="med" len="med"/>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="65" name="Shape 63">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000041000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvCxnSpPr/>
         </xdr:nvCxnSpPr>
         <xdr:spPr>
@@ -2618,20 +3034,26 @@
             <a:avLst/>
           </a:prstGeom>
           <a:noFill/>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="med" w="med" type="none"/>
-            <a:tailEnd len="med" w="med" type="none"/>
-          </a:ln>
-        </xdr:spPr>
-      </xdr:cxnSp>
-      <xdr:cxnSp>
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="64" name="Shape 64"/>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="med" len="med"/>
+            <a:tailEnd type="none" w="med" len="med"/>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="66" name="Shape 64">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000042000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvCxnSpPr/>
         </xdr:nvCxnSpPr>
         <xdr:spPr>
@@ -2643,20 +3065,26 @@
             <a:avLst/>
           </a:prstGeom>
           <a:noFill/>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="med" w="med" type="none"/>
-            <a:tailEnd len="med" w="med" type="none"/>
-          </a:ln>
-        </xdr:spPr>
-      </xdr:cxnSp>
-      <xdr:cxnSp>
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="65" name="Shape 65"/>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="med" len="med"/>
+            <a:tailEnd type="none" w="med" len="med"/>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="67" name="Shape 65">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000043000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvCxnSpPr/>
         </xdr:nvCxnSpPr>
         <xdr:spPr>
@@ -2668,20 +3096,26 @@
             <a:avLst/>
           </a:prstGeom>
           <a:noFill/>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="med" w="med" type="none"/>
-            <a:tailEnd len="med" w="med" type="none"/>
-          </a:ln>
-        </xdr:spPr>
-      </xdr:cxnSp>
-      <xdr:sp>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="med" len="med"/>
+            <a:tailEnd type="none" w="med" len="med"/>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:cxnSp>
+      <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="66" name="Shape 66"/>
+          <xdr:cNvPr id="68" name="Shape 66">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000044000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr txBox="1"/>
         </xdr:nvSpPr>
         <xdr:spPr>
@@ -2698,12 +3132,12 @@
           </a:ln>
         </xdr:spPr>
         <xdr:txBody>
-          <a:bodyPr anchorCtr="0" anchor="t" bIns="91425" lIns="91425" spcFirstLastPara="1" rIns="91425" wrap="square" tIns="91425">
+          <a:bodyPr spcFirstLastPara="1" wrap="square" lIns="91425" tIns="91425" rIns="91425" bIns="91425" anchor="t" anchorCtr="0">
             <a:noAutofit/>
           </a:bodyPr>
           <a:lstStyle/>
           <a:p>
-            <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+            <a:pPr marL="0" lvl="0" indent="0" algn="l" rtl="0">
               <a:spcBef>
                 <a:spcPts val="0"/>
               </a:spcBef>
@@ -2720,9 +3154,15 @@
           </a:p>
         </xdr:txBody>
       </xdr:sp>
-      <xdr:cxnSp>
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="67" name="Shape 67"/>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="69" name="Shape 67">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000045000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvCxnSpPr/>
         </xdr:nvCxnSpPr>
         <xdr:spPr>
@@ -2734,20 +3174,26 @@
             <a:avLst/>
           </a:prstGeom>
           <a:noFill/>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="med" w="med" type="none"/>
-            <a:tailEnd len="med" w="med" type="none"/>
-          </a:ln>
-        </xdr:spPr>
-      </xdr:cxnSp>
-      <xdr:cxnSp>
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="68" name="Shape 68"/>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="med" len="med"/>
+            <a:tailEnd type="none" w="med" len="med"/>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="70" name="Shape 68">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000046000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvCxnSpPr/>
         </xdr:nvCxnSpPr>
         <xdr:spPr>
@@ -2759,20 +3205,26 @@
             <a:avLst/>
           </a:prstGeom>
           <a:noFill/>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="med" w="med" type="none"/>
-            <a:tailEnd len="med" w="med" type="none"/>
-          </a:ln>
-        </xdr:spPr>
-      </xdr:cxnSp>
-      <xdr:sp>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="med" len="med"/>
+            <a:tailEnd type="none" w="med" len="med"/>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:cxnSp>
+      <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="69" name="Shape 69"/>
+          <xdr:cNvPr id="71" name="Shape 69">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000047000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr/>
         </xdr:nvSpPr>
         <xdr:spPr>
@@ -2786,23 +3238,23 @@
           <a:solidFill>
             <a:srgbClr val="FFFFFF"/>
           </a:solidFill>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="sm" w="sm" type="none"/>
-            <a:tailEnd len="sm" w="sm" type="none"/>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="sm" len="sm"/>
+            <a:tailEnd type="none" w="sm" len="sm"/>
           </a:ln>
         </xdr:spPr>
         <xdr:txBody>
-          <a:bodyPr anchorCtr="0" anchor="ctr" bIns="91425" lIns="91425" spcFirstLastPara="1" rIns="91425" wrap="square" tIns="91425">
+          <a:bodyPr spcFirstLastPara="1" wrap="square" lIns="91425" tIns="91425" rIns="91425" bIns="91425" anchor="ctr" anchorCtr="0">
             <a:noAutofit/>
           </a:bodyPr>
           <a:lstStyle/>
           <a:p>
-            <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="ctr">
+            <a:pPr marL="0" lvl="0" indent="0" algn="ctr" rtl="0">
               <a:spcBef>
                 <a:spcPts val="0"/>
               </a:spcBef>
@@ -2811,16 +3263,19 @@
               </a:spcAft>
               <a:buNone/>
             </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
             <a:endParaRPr sz="1400"/>
           </a:p>
         </xdr:txBody>
       </xdr:sp>
-      <xdr:cxnSp>
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="70" name="Shape 70"/>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="72" name="Shape 70">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000048000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvCxnSpPr>
             <a:stCxn id="69" idx="4"/>
           </xdr:cNvCxnSpPr>
@@ -2834,20 +3289,26 @@
             <a:avLst/>
           </a:prstGeom>
           <a:noFill/>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="med" w="med" type="none"/>
-            <a:tailEnd len="med" w="med" type="none"/>
-          </a:ln>
-        </xdr:spPr>
-      </xdr:cxnSp>
-      <xdr:cxnSp>
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="71" name="Shape 71"/>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="med" len="med"/>
+            <a:tailEnd type="none" w="med" len="med"/>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="73" name="Shape 71">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000049000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvCxnSpPr/>
         </xdr:nvCxnSpPr>
         <xdr:spPr>
@@ -2859,20 +3320,26 @@
             <a:avLst/>
           </a:prstGeom>
           <a:noFill/>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="med" w="med" type="none"/>
-            <a:tailEnd len="med" w="med" type="none"/>
-          </a:ln>
-        </xdr:spPr>
-      </xdr:cxnSp>
-      <xdr:cxnSp>
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="72" name="Shape 72"/>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="med" len="med"/>
+            <a:tailEnd type="none" w="med" len="med"/>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="74" name="Shape 72">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00004A000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvCxnSpPr/>
         </xdr:nvCxnSpPr>
         <xdr:spPr>
@@ -2884,20 +3351,26 @@
             <a:avLst/>
           </a:prstGeom>
           <a:noFill/>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="med" w="med" type="none"/>
-            <a:tailEnd len="med" w="med" type="none"/>
-          </a:ln>
-        </xdr:spPr>
-      </xdr:cxnSp>
-      <xdr:cxnSp>
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="73" name="Shape 73"/>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="med" len="med"/>
+            <a:tailEnd type="none" w="med" len="med"/>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="75" name="Shape 73">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00004B000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvCxnSpPr/>
         </xdr:nvCxnSpPr>
         <xdr:spPr>
@@ -2909,20 +3382,26 @@
             <a:avLst/>
           </a:prstGeom>
           <a:noFill/>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="med" w="med" type="none"/>
-            <a:tailEnd len="med" w="med" type="none"/>
-          </a:ln>
-        </xdr:spPr>
-      </xdr:cxnSp>
-      <xdr:sp>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="med" len="med"/>
+            <a:tailEnd type="none" w="med" len="med"/>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:cxnSp>
+      <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="74" name="Shape 74"/>
+          <xdr:cNvPr id="76" name="Shape 74">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00004C000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr/>
         </xdr:nvSpPr>
         <xdr:spPr>
@@ -2936,23 +3415,23 @@
           <a:solidFill>
             <a:srgbClr val="FFFFFF"/>
           </a:solidFill>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="sm" w="sm" type="none"/>
-            <a:tailEnd len="sm" w="sm" type="none"/>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="sm" len="sm"/>
+            <a:tailEnd type="none" w="sm" len="sm"/>
           </a:ln>
         </xdr:spPr>
         <xdr:txBody>
-          <a:bodyPr anchorCtr="0" anchor="ctr" bIns="91425" lIns="91425" spcFirstLastPara="1" rIns="91425" wrap="square" tIns="91425">
+          <a:bodyPr spcFirstLastPara="1" wrap="square" lIns="91425" tIns="91425" rIns="91425" bIns="91425" anchor="ctr" anchorCtr="0">
             <a:noAutofit/>
           </a:bodyPr>
           <a:lstStyle/>
           <a:p>
-            <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="ctr">
+            <a:pPr marL="0" lvl="0" indent="0" algn="ctr" rtl="0">
               <a:spcBef>
                 <a:spcPts val="0"/>
               </a:spcBef>
@@ -2961,16 +3440,19 @@
               </a:spcAft>
               <a:buNone/>
             </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
             <a:endParaRPr sz="1400"/>
           </a:p>
         </xdr:txBody>
       </xdr:sp>
-      <xdr:cxnSp>
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="75" name="Shape 75"/>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="77" name="Shape 75">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00004D000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvCxnSpPr>
             <a:stCxn id="74" idx="4"/>
           </xdr:cNvCxnSpPr>
@@ -2984,20 +3466,26 @@
             <a:avLst/>
           </a:prstGeom>
           <a:noFill/>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="med" w="med" type="none"/>
-            <a:tailEnd len="med" w="med" type="none"/>
-          </a:ln>
-        </xdr:spPr>
-      </xdr:cxnSp>
-      <xdr:cxnSp>
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="76" name="Shape 76"/>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="med" len="med"/>
+            <a:tailEnd type="none" w="med" len="med"/>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="78" name="Shape 76">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00004E000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvCxnSpPr/>
         </xdr:nvCxnSpPr>
         <xdr:spPr>
@@ -3009,20 +3497,26 @@
             <a:avLst/>
           </a:prstGeom>
           <a:noFill/>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="med" w="med" type="none"/>
-            <a:tailEnd len="med" w="med" type="none"/>
-          </a:ln>
-        </xdr:spPr>
-      </xdr:cxnSp>
-      <xdr:cxnSp>
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="77" name="Shape 77"/>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="med" len="med"/>
+            <a:tailEnd type="none" w="med" len="med"/>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="79" name="Shape 77">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00004F000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvCxnSpPr/>
         </xdr:nvCxnSpPr>
         <xdr:spPr>
@@ -3034,20 +3528,26 @@
             <a:avLst/>
           </a:prstGeom>
           <a:noFill/>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="med" w="med" type="none"/>
-            <a:tailEnd len="med" w="med" type="none"/>
-          </a:ln>
-        </xdr:spPr>
-      </xdr:cxnSp>
-      <xdr:cxnSp>
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="78" name="Shape 78"/>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="med" len="med"/>
+            <a:tailEnd type="none" w="med" len="med"/>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="80" name="Shape 78">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000050000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvCxnSpPr/>
         </xdr:nvCxnSpPr>
         <xdr:spPr>
@@ -3059,20 +3559,26 @@
             <a:avLst/>
           </a:prstGeom>
           <a:noFill/>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="med" w="med" type="none"/>
-            <a:tailEnd len="med" w="med" type="none"/>
-          </a:ln>
-        </xdr:spPr>
-      </xdr:cxnSp>
-      <xdr:sp>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="med" len="med"/>
+            <a:tailEnd type="none" w="med" len="med"/>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:cxnSp>
+      <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="79" name="Shape 79"/>
+          <xdr:cNvPr id="81" name="Shape 79">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000051000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr txBox="1"/>
         </xdr:nvSpPr>
         <xdr:spPr>
@@ -3089,12 +3595,12 @@
           </a:ln>
         </xdr:spPr>
         <xdr:txBody>
-          <a:bodyPr anchorCtr="0" anchor="t" bIns="91425" lIns="91425" spcFirstLastPara="1" rIns="91425" wrap="square" tIns="91425">
+          <a:bodyPr spcFirstLastPara="1" wrap="square" lIns="91425" tIns="91425" rIns="91425" bIns="91425" anchor="t" anchorCtr="0">
             <a:noAutofit/>
           </a:bodyPr>
           <a:lstStyle/>
           <a:p>
-            <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+            <a:pPr marL="0" lvl="0" indent="0" algn="l" rtl="0">
               <a:spcBef>
                 <a:spcPts val="0"/>
               </a:spcBef>
@@ -3111,9 +3617,15 @@
           </a:p>
         </xdr:txBody>
       </xdr:sp>
-      <xdr:sp>
+      <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="80" name="Shape 80"/>
+          <xdr:cNvPr id="82" name="Shape 80">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000052000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr txBox="1"/>
         </xdr:nvSpPr>
         <xdr:spPr>
@@ -3130,12 +3642,12 @@
           </a:ln>
         </xdr:spPr>
         <xdr:txBody>
-          <a:bodyPr anchorCtr="0" anchor="t" bIns="91425" lIns="91425" spcFirstLastPara="1" rIns="91425" wrap="square" tIns="91425">
+          <a:bodyPr spcFirstLastPara="1" wrap="square" lIns="91425" tIns="91425" rIns="91425" bIns="91425" anchor="t" anchorCtr="0">
             <a:noAutofit/>
           </a:bodyPr>
           <a:lstStyle/>
           <a:p>
-            <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+            <a:pPr marL="0" lvl="0" indent="0" algn="l" rtl="0">
               <a:spcBef>
                 <a:spcPts val="0"/>
               </a:spcBef>
@@ -3152,13 +3664,19 @@
           </a:p>
         </xdr:txBody>
       </xdr:sp>
-      <xdr:cxnSp>
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="81" name="Shape 81"/>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="83" name="Shape 81">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000053000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvCxnSpPr/>
         </xdr:nvCxnSpPr>
         <xdr:spPr>
-          <a:xfrm flipH="1" rot="10800000">
+          <a:xfrm rot="10800000" flipH="1">
             <a:off x="1963200" y="2308600"/>
             <a:ext cx="324900" cy="527700"/>
           </a:xfrm>
@@ -3166,20 +3684,26 @@
             <a:avLst/>
           </a:prstGeom>
           <a:noFill/>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="med" w="med" type="none"/>
-            <a:tailEnd len="med" w="med" type="none"/>
-          </a:ln>
-        </xdr:spPr>
-      </xdr:cxnSp>
-      <xdr:cxnSp>
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="82" name="Shape 82"/>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="med" len="med"/>
+            <a:tailEnd type="none" w="med" len="med"/>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="84" name="Shape 82">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000054000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvCxnSpPr/>
         </xdr:nvCxnSpPr>
         <xdr:spPr>
@@ -3191,20 +3715,26 @@
             <a:avLst/>
           </a:prstGeom>
           <a:noFill/>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="med" w="med" type="none"/>
-            <a:tailEnd len="med" w="med" type="none"/>
-          </a:ln>
-        </xdr:spPr>
-      </xdr:cxnSp>
-      <xdr:sp>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="med" len="med"/>
+            <a:tailEnd type="none" w="med" len="med"/>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:cxnSp>
+      <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="83" name="Shape 83"/>
+          <xdr:cNvPr id="85" name="Shape 83">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000055000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr/>
         </xdr:nvSpPr>
         <xdr:spPr>
@@ -3218,23 +3748,23 @@
           <a:solidFill>
             <a:srgbClr val="FFFFFF"/>
           </a:solidFill>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="sm" w="sm" type="none"/>
-            <a:tailEnd len="sm" w="sm" type="none"/>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="sm" len="sm"/>
+            <a:tailEnd type="none" w="sm" len="sm"/>
           </a:ln>
         </xdr:spPr>
         <xdr:txBody>
-          <a:bodyPr anchorCtr="0" anchor="ctr" bIns="91425" lIns="91425" spcFirstLastPara="1" rIns="91425" wrap="square" tIns="91425">
+          <a:bodyPr spcFirstLastPara="1" wrap="square" lIns="91425" tIns="91425" rIns="91425" bIns="91425" anchor="ctr" anchorCtr="0">
             <a:noAutofit/>
           </a:bodyPr>
           <a:lstStyle/>
           <a:p>
-            <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="ctr">
+            <a:pPr marL="0" lvl="0" indent="0" algn="ctr" rtl="0">
               <a:spcBef>
                 <a:spcPts val="0"/>
               </a:spcBef>
@@ -3243,16 +3773,19 @@
               </a:spcAft>
               <a:buNone/>
             </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
             <a:endParaRPr sz="1400"/>
           </a:p>
         </xdr:txBody>
       </xdr:sp>
-      <xdr:cxnSp>
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="84" name="Shape 84"/>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="86" name="Shape 84">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000056000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvCxnSpPr>
             <a:stCxn id="83" idx="4"/>
           </xdr:cNvCxnSpPr>
@@ -3266,20 +3799,26 @@
             <a:avLst/>
           </a:prstGeom>
           <a:noFill/>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="med" w="med" type="none"/>
-            <a:tailEnd len="med" w="med" type="none"/>
-          </a:ln>
-        </xdr:spPr>
-      </xdr:cxnSp>
-      <xdr:cxnSp>
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="85" name="Shape 85"/>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="med" len="med"/>
+            <a:tailEnd type="none" w="med" len="med"/>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="87" name="Shape 85">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000057000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvCxnSpPr/>
         </xdr:nvCxnSpPr>
         <xdr:spPr>
@@ -3291,20 +3830,26 @@
             <a:avLst/>
           </a:prstGeom>
           <a:noFill/>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="med" w="med" type="none"/>
-            <a:tailEnd len="med" w="med" type="none"/>
-          </a:ln>
-        </xdr:spPr>
-      </xdr:cxnSp>
-      <xdr:cxnSp>
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="86" name="Shape 86"/>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="med" len="med"/>
+            <a:tailEnd type="none" w="med" len="med"/>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="88" name="Shape 86">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000058000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvCxnSpPr/>
         </xdr:nvCxnSpPr>
         <xdr:spPr>
@@ -3316,20 +3861,26 @@
             <a:avLst/>
           </a:prstGeom>
           <a:noFill/>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="med" w="med" type="none"/>
-            <a:tailEnd len="med" w="med" type="none"/>
-          </a:ln>
-        </xdr:spPr>
-      </xdr:cxnSp>
-      <xdr:cxnSp>
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="87" name="Shape 87"/>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="med" len="med"/>
+            <a:tailEnd type="none" w="med" len="med"/>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="89" name="Shape 87">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000059000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvCxnSpPr/>
         </xdr:nvCxnSpPr>
         <xdr:spPr>
@@ -3341,20 +3892,26 @@
             <a:avLst/>
           </a:prstGeom>
           <a:noFill/>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="med" w="med" type="none"/>
-            <a:tailEnd len="med" w="med" type="none"/>
-          </a:ln>
-        </xdr:spPr>
-      </xdr:cxnSp>
-      <xdr:cxnSp>
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="88" name="Shape 88"/>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="med" len="med"/>
+            <a:tailEnd type="none" w="med" len="med"/>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="90" name="Shape 88">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00005A000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvCxnSpPr/>
         </xdr:nvCxnSpPr>
         <xdr:spPr>
@@ -3366,20 +3923,26 @@
             <a:avLst/>
           </a:prstGeom>
           <a:noFill/>
-          <a:ln cap="flat" cmpd="sng" w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="med" w="med" type="none"/>
-            <a:tailEnd len="med" w="med" type="none"/>
-          </a:ln>
-        </xdr:spPr>
-      </xdr:cxnSp>
-      <xdr:sp>
+          <a:ln w="9525" cap="flat" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="med" len="med"/>
+            <a:tailEnd type="none" w="med" len="med"/>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:cxnSp>
+      <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="89" name="Shape 89"/>
+          <xdr:cNvPr id="91" name="Shape 89">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00005B000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr txBox="1"/>
         </xdr:nvSpPr>
         <xdr:spPr>
@@ -3396,12 +3959,12 @@
           </a:ln>
         </xdr:spPr>
         <xdr:txBody>
-          <a:bodyPr anchorCtr="0" anchor="t" bIns="91425" lIns="91425" spcFirstLastPara="1" rIns="91425" wrap="square" tIns="91425">
+          <a:bodyPr spcFirstLastPara="1" wrap="square" lIns="91425" tIns="91425" rIns="91425" bIns="91425" anchor="t" anchorCtr="0">
             <a:noAutofit/>
           </a:bodyPr>
           <a:lstStyle/>
           <a:p>
-            <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+            <a:pPr marL="0" lvl="0" indent="0" algn="l" rtl="0">
               <a:spcBef>
                 <a:spcPts val="0"/>
               </a:spcBef>
@@ -3431,11 +3994,17 @@
     <xdr:ext cx="3438525" cy="3448050"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.png" title="Imagen"/>
+        <xdr:cNvPr id="92" name="image1.png" title="Imagen">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00005C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3459,11 +4028,17 @@
     <xdr:ext cx="3371850" cy="4191000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.png" title="Imagen"/>
+        <xdr:cNvPr id="93" name="image2.png" title="Imagen">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00005D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3487,11 +4062,17 @@
     <xdr:ext cx="3238500" cy="2800350"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image3.png" title="Imagen"/>
+        <xdr:cNvPr id="94" name="image3.png" title="Imagen">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00005E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3508,12 +4089,8 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -3703,23 +4280,26 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="B2:F8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col customWidth="1" min="3" max="3" width="33.5"/>
-    <col customWidth="1" min="4" max="4" width="15.63"/>
-    <col customWidth="1" min="5" max="5" width="12.38"/>
-    <col customWidth="1" min="6" max="6" width="18.88"/>
+    <col min="3" max="3" width="33.5" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" customWidth="1"/>
+    <col min="5" max="5" width="12.33203125" customWidth="1"/>
+    <col min="6" max="6" width="18.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2">
+    <row r="2" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -3736,7 +4316,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
@@ -3744,16 +4324,16 @@
         <v>6</v>
       </c>
       <c r="D3" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="E3" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="F3" s="2">
-        <v>16.0</v>
+        <v>16</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
@@ -3761,16 +4341,16 @@
         <v>8</v>
       </c>
       <c r="D4" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E4" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="F4" s="2">
-        <v>12.0</v>
+        <v>12</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B5" s="2" t="s">
         <v>9</v>
       </c>
@@ -3778,16 +4358,16 @@
         <v>10</v>
       </c>
       <c r="D5" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="E5" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="F5" s="2">
-        <v>8.0</v>
+        <v>8</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="2" t="s">
         <v>11</v>
       </c>
@@ -3795,47 +4375,48 @@
         <v>12</v>
       </c>
       <c r="D6" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E6" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="F6" s="2">
-        <v>12.0</v>
+        <v>12</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B8" s="2" t="s">
         <v>14</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:I20"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="8.38"/>
-    <col customWidth="1" min="2" max="2" width="49.88"/>
-    <col customWidth="1" min="3" max="3" width="22.75"/>
-    <col customWidth="1" min="4" max="4" width="19.13"/>
-    <col customWidth="1" min="5" max="5" width="18.0"/>
-    <col customWidth="1" min="6" max="8" width="39.75"/>
+    <col min="1" max="1" width="8.33203125" customWidth="1"/>
+    <col min="2" max="2" width="49.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.6640625" customWidth="1"/>
+    <col min="4" max="4" width="19.1640625" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="8" width="39.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:9" ht="13" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
         <v>15</v>
       </c>
@@ -3861,362 +4442,362 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5" t="s">
+    <row r="2" spans="1:9" ht="168" x14ac:dyDescent="0.15">
+      <c r="A2" s="11">
+        <v>0</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="3" ht="177.0" customHeight="1">
-      <c r="A3" s="6"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5" t="s">
+    <row r="3" spans="1:9" ht="177" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="12"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="8">
-        <v>1.0</v>
-      </c>
-      <c r="B4" s="9"/>
-      <c r="C4" s="5" t="s">
+    <row r="4" spans="1:9" ht="154" x14ac:dyDescent="0.15">
+      <c r="A4" s="13">
+        <v>1</v>
+      </c>
+      <c r="B4" s="15"/>
+      <c r="C4" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="4" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="5" ht="108.75" customHeight="1">
-      <c r="A5" s="10"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="5" t="s">
+    <row r="5" spans="1:9" ht="108.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="14"/>
+      <c r="B5" s="14"/>
+      <c r="C5" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H5" s="4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="10"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="5" t="s">
+    <row r="6" spans="1:9" ht="112" x14ac:dyDescent="0.15">
+      <c r="A6" s="14"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="G6" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="H6" s="4" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="6"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="5" t="s">
+    <row r="7" spans="1:9" ht="140" x14ac:dyDescent="0.15">
+      <c r="A7" s="12"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="G7" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="H7" s="4" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="8" ht="270.75" customHeight="1">
-      <c r="A8" s="11">
-        <v>2.0</v>
-      </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="12" t="s">
+    <row r="8" spans="1:9" ht="270.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="7">
+        <v>2</v>
+      </c>
+      <c r="B8" s="4"/>
+      <c r="C8" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="F8" s="12" t="s">
+      <c r="F8" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="G8" s="12" t="s">
+      <c r="G8" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="H8" s="4" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="13">
-        <v>3.0</v>
-      </c>
-      <c r="B9" s="9"/>
-      <c r="C9" s="12" t="s">
+    <row r="9" spans="1:9" ht="182" x14ac:dyDescent="0.15">
+      <c r="A9" s="16">
+        <v>3</v>
+      </c>
+      <c r="B9" s="15"/>
+      <c r="C9" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="E9" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="F9" s="12" t="s">
+      <c r="F9" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="G9" s="12" t="s">
+      <c r="G9" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="H9" s="12" t="s">
+      <c r="H9" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="I9" s="14"/>
+      <c r="I9" s="17"/>
     </row>
-    <row r="10">
-      <c r="A10" s="10"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="12" t="s">
+    <row r="10" spans="1:9" ht="112" x14ac:dyDescent="0.15">
+      <c r="A10" s="14"/>
+      <c r="B10" s="14"/>
+      <c r="C10" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="E10" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="F10" s="12" t="s">
+      <c r="F10" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="G10" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="G10" s="12" t="s">
+      <c r="H10" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="H10" s="12" t="s">
+      <c r="I10" s="17"/>
+    </row>
+    <row r="11" spans="1:9" ht="112" x14ac:dyDescent="0.15">
+      <c r="A11" s="14"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="I10" s="14"/>
+      <c r="D11" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="I11" s="17"/>
     </row>
-    <row r="11">
-      <c r="A11" s="10"/>
-      <c r="B11" s="10"/>
-      <c r="C11" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="D11" s="12" t="s">
+    <row r="12" spans="1:9" ht="126" x14ac:dyDescent="0.15">
+      <c r="A12" s="14"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="154" x14ac:dyDescent="0.15">
+      <c r="A13" s="14"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="D13" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E11" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="G11" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="H11" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="I11" s="14"/>
+      <c r="E13" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>84</v>
+      </c>
     </row>
-    <row r="12">
-      <c r="A12" s="10"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="E12" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="F12" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="G12" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="H12" s="12" t="s">
-        <v>81</v>
+    <row r="14" spans="1:9" ht="279.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="14"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>90</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="10"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="D13" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="E13" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="F13" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="G13" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="H13" s="12" t="s">
-        <v>86</v>
-      </c>
+    <row r="15" spans="1:9" ht="13" x14ac:dyDescent="0.15">
+      <c r="A15" s="5"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10"/>
     </row>
-    <row r="14" ht="279.75" customHeight="1">
-      <c r="A14" s="10"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="D14" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E14" s="15" t="s">
-        <v>89</v>
-      </c>
-      <c r="F14" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="G14" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="H14" s="15" t="s">
-        <v>92</v>
-      </c>
+    <row r="16" spans="1:9" ht="13" x14ac:dyDescent="0.15">
+      <c r="A16" s="5"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
     </row>
-    <row r="15">
-      <c r="A15" s="7"/>
-      <c r="B15" s="16"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="16"/>
+    <row r="17" spans="1:8" ht="13" x14ac:dyDescent="0.15">
+      <c r="A17" s="5"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
     </row>
-    <row r="16">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
+    <row r="18" spans="1:8" ht="13" x14ac:dyDescent="0.15">
+      <c r="A18" s="5"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
     </row>
-    <row r="17">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
+    <row r="19" spans="1:8" ht="13" x14ac:dyDescent="0.15">
+      <c r="A19" s="5"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
     </row>
-    <row r="18">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
+    <row r="20" spans="1:8" ht="13" x14ac:dyDescent="0.15">
+      <c r="A20" s="5"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -4226,9 +4807,9 @@
     <mergeCell ref="A9:A14"/>
     <mergeCell ref="B9:B13"/>
   </mergeCells>
-  <printOptions gridLines="1" horizontalCentered="1"/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup fitToHeight="0" paperSize="9" cellComments="atEnd" orientation="landscape" pageOrder="overThenDown"/>
+  <printOptions horizontalCentered="1" gridLines="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup paperSize="9" fitToHeight="0" pageOrder="overThenDown" orientation="landscape" cellComments="atEnd"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>